--- a/pensum/ol19/OL19_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol19/OL19_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="154">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 19: Organisasjonskultur (V5)</t>
   </si>
@@ -146,9 +146,18 @@
     <t xml:space="preserve">a)  Hvor mange prosent av de 32 avvikene i fjor ble meldt av noen andre enn den som selv gjorde feilen? Én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andel = avvik meldt av andre / alle avvik × 100. Begrepet bak er at kulturen avgjør hvordan de formelle oppgavene løses (Organisasjon og ledelse 19.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor mange kroner i fakturerbar tid kostet omgjøringen? 2 montører × 2 dager × 8 timer × 890 kr.</t>
   </si>
   <si>
+    <t xml:space="preserve">Tapt fakturering = antall montører × dager × timer per dag × timepris. Timeprisen er fra Nordlys' faktaark; regnestykket er casens, ikke bokas.</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Alle avdelingene har samme avviksskjema, samme HMS-perm og samme daglige leder. Hva forklarer best at prosjekt og nybygg melder 2 av 9 egne feil og solcelle og lading 5 av 6?   A: Strukturen: avdelingene har ulike rutiner for avvik   B: Kulturen: ulike uformelle normer for hva som skjer med den som sier fra   C: Kompetansen: montørene i prosjekt er dårligere fagfolk   (skriv bokstaven)</t>
   </si>
   <si>
@@ -173,6 +182,24 @@
     <t xml:space="preserve">e)  Montøren sier «Jeg tenkte det ordnet seg.» Tom vil gi ham en advarsel og sende ut en påminnelse om at avvik skal meldes. Hva sier kapitlet om de to tiltakene, og hva bør Kari gjøre i stedet? Tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Bruk verdi og norm, sanksjoner (19.1) og Scheins syn på kultur som lært og som består så lenge den oppfattes som riktig (19.1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meldt av andre: 32 − 18 = 14 avvik, delt på 32. Omgjøringen: 2 montører × 2 dager × 8 timer, ganger timeprisen 890 kr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verdi eller norm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En verdi er det vi sier er godt. En norm er en regel for hva som er akseptabelt, og brudd gir en reaksjon. Formelle normer er regler, rutiner og prosedyrer.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 19, avsnitt 19.1 (definisjonen, verdier og normer, formelle og uformelle normer, sanksjoner, Scheins definisjon). Avvikstallene er fra sammendraget og appen; timeprisen fra faktaarket. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -266,6 +293,21 @@
     <t xml:space="preserve">e)  Hva kommer lærlingen til å lære om sjekklista de første ukene, og hva bør Mona gjøre før hun begynner? Bruk Schein og skillet mellom verdi og norm. Tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Bruk verdi og norm, virkelighetsoppfatninger og sosialisering (19.1), og artefaktene (19.2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tre lag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Det du ser og hører (logo, klær, språk, historier) er kulturelle symboler. Det som sies er godt, er verdier. Det som tas for gitt uten å sies, er virkelighetsoppfatninger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lærlingen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schein: kulturen læres bort til nye som den riktige måten. Lærer lærlingen det som blir sagt, eller det montøren gjør når det haster?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 19, avsnitt 19.1 (verdier, normer, virkelighetsoppfatninger, Scheins definisjon og sosialisering) og 19.2 (kulturelle symboler, symbolsk og instrumentell verdi). Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -302,9 +344,15 @@
     <t xml:space="preserve">a)  Hvis den nye avdelingen hadde meldt som de to gjorde i fjor: hvor mange prosent av avvikene ville vært meldt av den som selv gjorde feilen? (11 + 5) / (17 + 6). Én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Andel egne avvik = egne avvik / alle avvik × 100. Tallet forutsetter at begge gruppene beholder sin måte å melde på; det er casens regnestykke, ikke bokas.</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Den nye avdelingen får 7 utførende under Tom. Hvor mange prosent av dem kommer fra solcelle og lading? Én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Andel = antall fra gruppen / alle i avdelingen × 100. Begrepet bak er kulturell kongruens: hvor utbredt en bestemt kultur er (Organisasjon og ledelse 19.4).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Ja eller nei: er dette en av de tre måtene organisasjonsstrukturen skaper subkulturer på (19.4)?</t>
   </si>
   <si>
@@ -329,6 +377,18 @@
     <t xml:space="preserve">e)  Hvis Kari velger sammenslåingen: hvordan bør hun og Tom gjennomføre den, slik at meldekulturen fra solcelle og lading ikke forsvinner? Og hva taler for å ansette en egen leder i stedet? Bruk minst ett tall og to av virkemidlene fra kapitlet. Tre–fire setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Bruk ledelsens bevisste kulturbygging med riter og sosialisering (19.3.2), subkultur og motkultur (19.4) og Scheins syn på kultur som lært (19.1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egne i ny avdeling: (11 + 5) delt på (17 + 6). Fra solcelle: 2 delt på 7. Svar i prosent med én desimal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subkultur eller motkultur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boka gir tre måter strukturen skaper subkulturer på. En motkultur står for noe vesentlig annet på viktige områder. Hva står de to på solcelle for?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 19, avsnitt 19.3.2 (ledelsens bevisste kulturbygging, riter og sosialisering), 19.4 (kulturell styrke og kongruens, subkulturer, tre måter strukturen skaper subkulturer, motkultur) og 19.1 (Schein: kulturen består så lenge den oppfattes som riktig). Avvikstallene er fra sammendraget og appen. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -401,10 +461,28 @@
     <t xml:space="preserve">c)  Hvor mange prosent av de fem i Fjell er nye etter sommeren?</t>
   </si>
   <si>
+    <t xml:space="preserve">Andel nye = antall nye / alle × 100. Begrepet bak er sosialisering av nye medarbeidere (Organisasjon og ledelse 19.1 og 19.3.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Mona sier: «Vi tre er alltid enige. Vi har en sterk kultur.» Hva sier kapitlet om det?   A: Enighet viser at kulturen er sterk og trygg   B: Rask enighet kan være gruppetenkning, som lettere oppstår i sterke kulturer og sjelden merkes mens det skjer   C: Gruppetenkning finnes bare i store organisasjoner   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Hva bør Mona gjøre de første ukene etter sommeren, slik at de to nye lærer de riktige normene og tør å si imot? Bruk minst to av virkemidlene fra kapitlet. Tre setninger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingen ny formel. Bruk riter og sosialisering (19.3.2), tabula rasa (19.3.1) og gruppetenkning (19.5).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hva Mona styrer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tre kilder til kultur: nasjonal kultur, ledelsen og markedet. Bare den midterste kan Mona styre: riter, sosialisering og rekruttering. Nye: 2 av 5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alltid enige</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gruppetenkning setter konsensus framfor alt, oppstår lettere i sterke kulturer og merkes sjelden mens det skjer. Hvem på morgenmøtet tør å si imot?</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 19, avsnitt 19.3.1 (nasjonal kultur, tabula rasa), 19.3.2 (ledelsens bevisste kulturbygging: riter, sosialisering, rekruttering), 19.3.3 (markedet) og 19.5 (sterk kultur og gruppetenkning). Fjell Elektro AS er en konstruert casebedrift.</t>
@@ -418,7 +496,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -485,8 +563,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -502,13 +602,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFF4F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -561,7 +679,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -646,11 +764,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -695,8 +833,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -710,7 +848,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -724,7 +862,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1027,7 +1165,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1181,33 +1319,18 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="20" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(28480))&lt;=1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+      <c r="B18" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="20" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
     </row>
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
@@ -1217,154 +1340,251 @@
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+      <c r="F20" s="18"/>
+      <c r="G20" s="20" t="str">
+        <f aca="false">IF(F20="","",IF(ABS(F20-(28480))&lt;=1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="20" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+    </row>
+    <row r="23" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="20" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="21"/>
+      <c r="F23" s="23"/>
       <c r="G23" s="20" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="20" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="21"/>
+      <c r="F25" s="23"/>
       <c r="G25" s="20" t="str">
         <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-    </row>
-    <row r="31" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+      <c r="F26" s="23"/>
+      <c r="G26" s="20" t="str">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="20" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="20" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="20" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="24"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="24"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="24"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="27"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+    </row>
+    <row r="41" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="23">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:G29"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1381,7 +1601,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1392,7 +1612,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1402,7 +1622,7 @@
     </row>
     <row r="4" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1413,7 +1633,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1424,10 +1644,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
@@ -1436,11 +1656,11 @@
       <c r="G7" s="19"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23" t="s">
-        <v>56</v>
+      <c r="A8" s="28" t="s">
+        <v>65</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1449,11 +1669,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23" t="s">
-        <v>58</v>
+      <c r="A9" s="28" t="s">
+        <v>67</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1462,11 +1682,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23" t="s">
-        <v>60</v>
+      <c r="A10" s="28" t="s">
+        <v>69</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1475,11 +1695,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23" t="s">
-        <v>62</v>
+      <c r="A11" s="28" t="s">
+        <v>71</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1488,11 +1708,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="s">
-        <v>64</v>
+      <c r="A12" s="28" t="s">
+        <v>73</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1501,11 +1721,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="s">
-        <v>66</v>
+      <c r="A13" s="28" t="s">
+        <v>75</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1514,11 +1734,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23" t="s">
-        <v>68</v>
+      <c r="A14" s="28" t="s">
+        <v>77</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1543,13 +1763,13 @@
     </row>
     <row r="17" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="21"/>
+      <c r="F17" s="23"/>
       <c r="G17" s="20" t="str">
         <f aca="false">IF(F17="","",IF(UPPER(TRIM(F17))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1557,7 +1777,7 @@
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1566,13 +1786,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="21"/>
+      <c r="F19" s="23"/>
       <c r="G19" s="20" t="str">
         <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1580,13 +1800,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="21"/>
+      <c r="F20" s="23"/>
       <c r="G20" s="20" t="str">
         <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1594,13 +1814,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="21"/>
+      <c r="F21" s="23"/>
       <c r="G21" s="20" t="str">
         <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1608,13 +1828,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="21"/>
+      <c r="F22" s="23"/>
       <c r="G22" s="20" t="str">
         <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1622,13 +1842,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="21"/>
+      <c r="F23" s="23"/>
       <c r="G23" s="20" t="str">
         <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1636,13 +1856,13 @@
     </row>
     <row r="24" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="21"/>
+      <c r="F24" s="23"/>
       <c r="G24" s="20" t="str">
         <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1650,13 +1870,13 @@
     </row>
     <row r="25" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="21"/>
+      <c r="F25" s="23"/>
       <c r="G25" s="20" t="str">
         <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="C","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1664,7 +1884,7 @@
     </row>
     <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -1672,56 +1892,106 @@
       <c r="E26" s="7"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
+      <c r="A27" s="24"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
+      <c r="A28" s="24"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-    </row>
-    <row r="31" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+    </row>
+    <row r="37" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="28">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1744,8 +2014,12 @@
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:G29"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1762,7 +2036,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1773,7 +2047,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1783,7 +2057,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1794,7 +2068,7 @@
     </row>
     <row r="5" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1805,21 +2079,21 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>5</v>
@@ -1846,22 +2120,22 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="B10" s="25" t="n">
+      <c r="A10" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="30" t="n">
         <v>23</v>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="30" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
@@ -1869,7 +2143,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -1903,7 +2177,7 @@
     </row>
     <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -1915,190 +2189,272 @@
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="20" t="str">
-        <f aca="false">IF(F17="","",IF(ABS(F17-(28.6))&lt;=0.1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+    </row>
+    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="21"/>
+      <c r="F19" s="18"/>
       <c r="G19" s="20" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="20" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="20" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F19="","",IF(ABS(F19-(28.6))&lt;=0.1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+    </row>
+    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="20" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="21"/>
+      <c r="F23" s="23"/>
       <c r="G23" s="20" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="21"/>
+      <c r="F24" s="23"/>
       <c r="G24" s="20" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="C","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-    </row>
-    <row r="30" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="20" t="str">
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="20" t="str">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="20" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="20" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="C","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="24"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="24"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="24"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C37" s="27"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+    </row>
+    <row r="40" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="23">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="B17:G17"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:G28"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2115,7 +2471,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2126,7 +2482,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2136,7 +2492,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2147,7 +2503,7 @@
     </row>
     <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2158,10 +2514,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
@@ -2170,11 +2526,11 @@
       <c r="G7" s="19"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23" t="s">
-        <v>105</v>
+      <c r="A8" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2183,11 +2539,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23" t="s">
-        <v>68</v>
+      <c r="A9" s="28" t="s">
+        <v>77</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2196,11 +2552,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23" t="s">
-        <v>108</v>
+      <c r="A10" s="28" t="s">
+        <v>128</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2209,11 +2565,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23" t="s">
-        <v>110</v>
+      <c r="A11" s="28" t="s">
+        <v>130</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2222,11 +2578,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="s">
-        <v>112</v>
+      <c r="A12" s="28" t="s">
+        <v>132</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2235,11 +2591,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="28" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2248,11 +2604,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23" t="s">
-        <v>115</v>
+      <c r="A14" s="28" t="s">
+        <v>135</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -2277,13 +2633,13 @@
     </row>
     <row r="17" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="21"/>
+      <c r="F17" s="23"/>
       <c r="G17" s="20" t="str">
         <f aca="false">IF(F17="","",IF(UPPER(TRIM(F17))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2291,7 +2647,7 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -2300,13 +2656,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="21"/>
+      <c r="F19" s="23"/>
       <c r="G19" s="20" t="str">
         <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2314,13 +2670,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="21"/>
+      <c r="F20" s="23"/>
       <c r="G20" s="20" t="str">
         <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2328,13 +2684,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="21"/>
+      <c r="F21" s="23"/>
       <c r="G21" s="20" t="str">
         <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2342,13 +2698,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="21"/>
+      <c r="F22" s="23"/>
       <c r="G22" s="20" t="str">
         <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2356,13 +2712,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="21"/>
+      <c r="F23" s="23"/>
       <c r="G23" s="20" t="str">
         <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2370,7 +2726,7 @@
     </row>
     <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2382,80 +2738,143 @@
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="20" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+    </row>
+    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="20" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-    </row>
-    <row r="31" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="24"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="24"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B36" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="B37" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C37" s="27"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+    </row>
+    <row r="39" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="29">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2475,11 +2894,16 @@
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:G29"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ol19/OL19_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol19/OL19_Klasseoppgaver_v5.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Kort oppsummert: Organisasjonskultur er det sett av verdier, normer og virkelighetsoppfatninger som preger organisasjonen (19.1). Kulturen har stor innvirkning på hvordan de formelle oppgavene løses. En verdi er det som holdes for verdifullt, ønskelig og godt. En norm er en uskreven regel for hva som er akseptabel atferd i en bestemt situasjon; brudd fører ofte til sanksjoner. Formelle normer er regler, rutiner og prosedyrer; uformelle normer er skikk og bruk. Schein: kulturen er lært, og læres bort til nye som den riktige måten å tenke og føle på.</t>
   </si>
   <si>
-    <t xml:space="preserve">Casen er lagt til 2026/2027. Nordlys meldte 32 avvik i fjor. Alle avdelingene har samme avviksskjema, samme HMS-perm og samme daglige leder. I solcelle og lading ble 5 av 6 avvik meldt av den som selv hadde gjort feilen, i service 11 av 17 og i prosjekt og nybygg 2 av 9. På et nybygg la en montør om en kursfordeling fordi skapet var for lite, uten å rette kursfortegnelsen. Feilen ble oppdaget ved sluttkontrollen 11 uker senere, og omgjøringen tok 2 montører 2 dager à 8 timer. Timeprisen er 890 kr uten mva. Montøren sier: «Jeg tenkte det ordnet seg.» Tom vil gi ham en advarsel og sende ut en påminnelse om at avvik skal meldes. Gå fram slik: regn andelen avvik som ble meldt av andre, regn hva feilen kostet, forklar forskjellen mellom avdelingene, sorter verdier og normer, og vurder Toms forslag.</t>
+    <t xml:space="preserve">Casen er lagt til 2026/2027. Nordlys meldte 32 avvik i fjor. Alle avdelingene har samme avviksskjema, samme perm for helse, miljø og sikkerhet (HMS) og samme daglige leder. I solcelle og lading ble 5 av 6 avvik meldt av den som selv hadde gjort feilen, i service 11 av 17 og i prosjekt og nybygg 2 av 9. På et nybygg la en montør om en kursfordeling fordi skapet var for lite, uten å rette kursfortegnelsen. Feilen ble oppdaget ved sluttkontrollen 11 uker senere, og omgjøringen tok 2 montører 2 dager à 8 timer. Timeprisen er 890 kr uten merverdiavgift. Montøren sier: «Jeg tenkte det ordnet seg.» Tom vil gi ham en advarsel og sende ut en påminnelse om at avvik skal meldes. Gå fram slik: regn andelen avvik som ble meldt av andre, regn hva feilen kostet, forklar forskjellen mellom avdelingene, sorter verdier og normer, og vurder Toms forslag.</t>
   </si>
   <si>
     <t xml:space="preserve">Avdeling</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">Omgjøringen: 2 montører × 2 dager</t>
   </si>
   <si>
-    <t xml:space="preserve">8 t/dag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">890 kr/t</t>
+    <t xml:space="preserve">8 timer per dag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">890 kr per time</t>
   </si>
   <si>
     <t xml:space="preserve">Meldt av andre, % av alle</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">Tapt fakturering = antall montører × dager × timer per dag × timepris. Timeprisen er fra Nordlys' faktaark; regnestykket er casens, ikke bokas.</t>
   </si>
   <si>
-    <t xml:space="preserve">c)  Alle avdelingene har samme avviksskjema, samme HMS-perm og samme daglige leder. Hva forklarer best at prosjekt og nybygg melder 2 av 9 egne feil og solcelle og lading 5 av 6?   A: Strukturen: avdelingene har ulike rutiner for avvik   B: Kulturen: ulike uformelle normer for hva som skjer med den som sier fra   C: Kompetansen: montørene i prosjekt er dårligere fagfolk   (skriv bokstaven)</t>
+    <t xml:space="preserve">c)  Alle avdelingene har samme avviksskjema, samme perm for helse, miljø og sikkerhet og samme daglige leder. Hva forklarer best at prosjekt og nybygg melder 2 av 9 egne feil og solcelle og lading 5 av 6?   A: Strukturen: avdelingene har ulike rutiner for avvik   B: Kulturen: ulike uformelle normer for hva som skjer med den som sier fra   C: Kompetansen: montørene i prosjekt er dårligere fagfolk   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Ja eller nei: er dette en norm, altså en regel for hva som er akseptabel atferd i en bestemt situasjon, og ikke en verdi?</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">      «Du melder fra hvis noen andre ser det først»   (Ja eller Nei)</t>
   </si>
   <si>
-    <t xml:space="preserve">      Avviksprosedyren i HMS-permen   (Ja eller Nei)</t>
+    <t xml:space="preserve">      Avviksprosedyren i permen for helse, miljø og sikkerhet   (Ja eller Nei)</t>
   </si>
   <si>
     <t xml:space="preserve">      Den som kommer sist til basen, fyller bilen   (Ja eller Nei)</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">      Hver avdeling legger bare merke til informasjon som er nyttig for seg   (Ja eller Nei)</t>
   </si>
   <si>
-    <t xml:space="preserve">      Alle avdelingene har samme HMS-perm   (Ja eller Nei)</t>
+    <t xml:space="preserve">      Alle avdelingene har samme perm for helse, miljø og sikkerhet   (Ja eller Nei)</t>
   </si>
   <si>
     <t xml:space="preserve">      Alle har arbeidstøy med samme logo   (Ja eller Nei)</t>

--- a/pensum/ol19/OL19_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol19/OL19_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="154">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 19: Organisasjonskultur (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 19: Organisasjonskultur (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>

--- a/pensum/ol19/OL19_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol19/OL19_Klasseoppgaver_v5.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Kort oppsummert: Organisasjonskultur er det sett av verdier, normer og virkelighetsoppfatninger som preger organisasjonen (19.1). Kulturen har stor innvirkning på hvordan de formelle oppgavene løses. En verdi er det som holdes for verdifullt, ønskelig og godt. En norm er en uskreven regel for hva som er akseptabel atferd i en bestemt situasjon; brudd fører ofte til sanksjoner. Formelle normer er regler, rutiner og prosedyrer; uformelle normer er skikk og bruk. Schein: kulturen er lært, og læres bort til nye som den riktige måten å tenke og føle på.</t>
   </si>
   <si>
-    <t xml:space="preserve">Casen er lagt til 2026/2027. Nordlys meldte 32 avvik i fjor. Alle avdelingene har samme avviksskjema, samme perm for helse, miljø og sikkerhet (HMS) og samme daglige leder. I solcelle og lading ble 5 av 6 avvik meldt av den som selv hadde gjort feilen, i service 11 av 17 og i prosjekt og nybygg 2 av 9. På et nybygg la en montør om en kursfordeling fordi skapet var for lite, uten å rette kursfortegnelsen. Feilen ble oppdaget ved sluttkontrollen 11 uker senere, og omgjøringen tok 2 montører 2 dager à 8 timer. Timeprisen er 890 kr uten merverdiavgift. Montøren sier: «Jeg tenkte det ordnet seg.» Tom vil gi ham en advarsel og sende ut en påminnelse om at avvik skal meldes. Gå fram slik: regn andelen avvik som ble meldt av andre, regn hva feilen kostet, forklar forskjellen mellom avdelingene, sorter verdier og normer, og vurder Toms forslag.</t>
+    <t xml:space="preserve">Casen er lagt til 2026/2027. Nordlys meldte 32 avvik i fjor. Alle avdelingene har samme avviksskjema, samme perm for helse, miljø og sikkerhet (HMS) og samme daglige leder. I solcelle og lading ble 5 av 6 avvik meldt av den som selv hadde gjort feilen, i service 11 av 17 og i prosjekt og nybygg 2 av 9. På et nybygg la en montør om en kursfordeling fordi skapet var for lite, uten å rette kursfortegnelsen. Feilen ble oppdaget ved sluttkontrollen 11 uker senere, og omgjøringen tok 2 montører 2 dager à 8 timer. Timeprisen Nordlys tar av kunden, er 890 kr uten merverdiavgift (faktaarket). Montøren sier: «Jeg tenkte det ordnet seg.» Tom vil gi ham en advarsel og sende ut en påminnelse om at avvik skal meldes. Gå fram slik: regn andelen avvik som ble meldt av andre, regn hva feilen kostet, forklar forskjellen mellom avdelingene, sorter verdier og normer, og vurder Toms forslag.</t>
   </si>
   <si>
     <t xml:space="preserve">Avdeling</t>
@@ -1195,7 +1195,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>23</v>
       </c>
